--- a/BOM/BOM_PCB_2026-06-03.xlsx
+++ b/BOM/BOM_PCB_2026-06-03.xlsx
@@ -1,13 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEBE48D-A892-466E-8910-FD8231A8EEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="bom模板" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Field汇总" state="visible" r:id="rId5"/>
+    <sheet name="bom模板" sheetId="1" r:id="rId1"/>
+    <sheet name="Field汇总" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -797,30 +814,37 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="¥#,##0.00;¥-#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="\¥#,##0.00;\¥\-#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <name val="等线"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -838,7 +862,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,23 +877,37 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -878,12 +916,6 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -893,13 +925,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -925,13 +963,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1128346</xdr:colOff>
+      <xdr:colOff>551324</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>105091</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -1284,34 +1322,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L62"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.25" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="13.125" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="14.375" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
-    <col min="9" max="9" width="13.375" customWidth="1"/>
-    <col min="10" max="10" width="14.375" customWidth="1"/>
-    <col min="11" max="11" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.08984375" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="2" t="s">
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
@@ -1329,17 +1367,17 @@
       <c r="K1" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
       <c r="G2" t="s">
         <v>0</v>
       </c>
@@ -1355,16 +1393,16 @@
       <c r="K2" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="4" t="s">
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" t="s">
@@ -1385,16 +1423,16 @@
       <c r="K3" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="4" t="s">
+      <c r="L3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
@@ -1415,16 +1453,16 @@
       <c r="K4" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="4" t="s">
+      <c r="L4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
@@ -1445,2144 +1483,2256 @@
       <c r="K5" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="L5" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B7" s="9">
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <f t="shared" ref="A7:A38" si="0">ROW()-6</f>
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="F7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <f>B7*K7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B8" s="9">
+      <c r="J7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="e">
+        <f t="shared" ref="L7:L38" si="1">B7*K7</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="7">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="F8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <f>B8*K8</f>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B9" s="9">
+      <c r="J8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
         <v>1</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="F9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10">
-        <f>B9*K9</f>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B10" s="9">
+      <c r="J9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="7">
         <v>3</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10">
-        <f>B10*K10</f>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B11" s="9">
+      <c r="J10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <f>B11*K11</f>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B12" s="9">
+      <c r="G11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="7">
         <v>4</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
-        <f>B12*K12</f>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B13" s="9">
+      <c r="G12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="7">
         <v>1</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <f>B13*K13</f>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B14" s="9">
+      <c r="G13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="7">
         <v>4</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <f>B14*K14</f>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B15" s="9">
+      <c r="J14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <f>B15*K15</f>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B16" s="9">
+      <c r="J15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="7">
         <v>5</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10">
-        <f>B16*K16</f>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B17" s="9">
+      <c r="G16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="7">
         <v>1</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="F17" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L17" s="10">
-        <f>B17*K17</f>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B18" s="9">
+      <c r="J17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="7">
         <v>1</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L18" s="10">
-        <f>B18*K18</f>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B19" s="9">
+      <c r="J18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="7">
         <v>1</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L19" s="10">
-        <f>B19*K19</f>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B20" s="9">
+      <c r="J19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="7">
         <v>1</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L20" s="10">
-        <f>B20*K20</f>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B21" s="9">
+      <c r="G20" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="7">
         <v>2</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L21" s="10">
-        <f>B21*K21</f>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B22" s="9">
+      <c r="J21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="7">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9" t="s">
+      <c r="F22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L22" s="10">
-        <f>B22*K22</f>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B23" s="9">
+      <c r="J22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="7">
         <v>1</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="F23" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L23" s="10">
-        <f>B23*K23</f>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B24" s="9">
+      <c r="J23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="7">
         <v>1</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9" t="s">
+      <c r="F24" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L24" s="10">
-        <f>B24*K24</f>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B25" s="9">
+      <c r="J24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="7">
         <v>1</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9" t="s">
+      <c r="F25" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10">
-        <f>B25*K25</f>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B26" s="9">
+      <c r="J25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="7">
         <v>1</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9" t="s">
+      <c r="F26" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L26" s="10">
-        <f>B26*K26</f>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B27" s="9">
+      <c r="J26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="7">
         <v>3</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9" t="s">
+      <c r="F27" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10">
-        <f>B27*K27</f>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B28" s="9">
+      <c r="J27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="7">
         <v>1</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="9" t="s">
+      <c r="F28" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L28" s="10">
-        <f>B28*K28</f>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B29" s="9">
+      <c r="J28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="7">
         <v>1</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9" t="s">
+      <c r="F29" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10">
-        <f>B29*K29</f>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B30" s="9">
+      <c r="J29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="7">
         <v>1</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="F30" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L30" s="10">
-        <f>B30*K30</f>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B31" s="9">
+      <c r="J30" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="7">
         <v>1</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9" t="s">
+      <c r="F31" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L31" s="10">
-        <f>B31*K31</f>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B32" s="9">
+      <c r="J31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="7">
         <v>1</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" s="9" t="s">
+      <c r="F32" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J32" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L32" s="10">
-        <f>B32*K32</f>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B33" s="9">
+      <c r="J32" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="7">
         <v>3</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="F33" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L33" s="10">
-        <f>B33*K33</f>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B34" s="9">
+      <c r="J33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="7">
         <v>1</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J34" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L34" s="10">
-        <f>B34*K34</f>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B35" s="9">
+      <c r="J34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="7">
         <v>1</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="F35" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L35" s="10">
-        <f>B35*K35</f>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B36" s="9">
+      <c r="J35" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="7">
         <v>2</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="9" t="s">
+      <c r="F36" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J36" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L36" s="10">
-        <f>B36*K36</f>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B37" s="9">
+      <c r="J36" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="6">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="7">
         <v>1</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L37" s="10">
-        <f>B37*K37</f>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B38" s="9">
+      <c r="G37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="6">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="7">
         <v>1</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L38" s="10">
-        <f>B38*K38</f>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B39" s="9">
+      <c r="G38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="6">
+        <f t="shared" ref="A39:A62" si="2">ROW()-6</f>
+        <v>33</v>
+      </c>
+      <c r="B39" s="7">
         <v>2</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I39" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="J39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L39" s="10">
-        <f>B39*K39</f>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B40" s="9">
+      <c r="J39" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="e">
+        <f t="shared" ref="L39:L70" si="3">B39*K39</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="7">
         <v>2</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I40" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J40" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L40" s="10">
-        <f>B40*K40</f>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B41" s="9">
+      <c r="J40" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="7">
         <v>1</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L41" s="10">
-        <f>B41*K41</f>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B42" s="9">
+      <c r="G41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="6">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="7">
         <v>5</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="G42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L42" s="10">
-        <f>B42*K42</f>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B43" s="9">
+      <c r="G42" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="6">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="7">
         <v>2</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G43" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L43" s="10">
-        <f>B43*K43</f>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B44" s="9">
+      <c r="G43" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="6">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="7">
         <v>2</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="G44" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L44" s="10">
-        <f>B44*K44</f>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B45" s="9">
+      <c r="G44" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L44" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="6">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="7">
         <v>1</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" s="9" t="s">
+      <c r="F45" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="J45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L45" s="10">
-        <f>B45*K45</f>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B46" s="9">
+      <c r="J45" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="J46" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L46" s="10">
-        <f>B46*K46</f>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B47" s="9">
+      <c r="J46" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="6">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="7">
         <v>2</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="F47" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="J47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L47" s="10">
-        <f>B47*K47</f>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B48" s="9">
+      <c r="J47" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L48" s="10">
-        <f>B48*K48</f>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B49" s="9">
+      <c r="F48" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="7">
         <v>1</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="F49" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="J49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L49" s="10">
-        <f>B49*K49</f>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B50" s="9">
+      <c r="J49" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="7">
         <v>2</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" s="9" t="s">
+      <c r="F50" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="J50" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L50" s="10">
-        <f>B50*K50</f>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B51" s="9">
+      <c r="J50" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="6">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G51" s="9" t="s">
+      <c r="F51" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I51" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="J51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L51" s="10">
-        <f>B51*K51</f>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B52" s="9">
+      <c r="J51" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="6">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="7">
         <v>1</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F52" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G52" s="9" t="s">
+      <c r="F52" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J52" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L52" s="10">
-        <f>B52*K52</f>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B53" s="9">
+      <c r="J52" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L52" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="6">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="7">
         <v>1</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="I53" s="9" t="s">
+      <c r="I53" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K53" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L53" s="10">
-        <f>B53*K53</f>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B54" s="9">
+      <c r="J53" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="6">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="7">
         <v>1</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F54" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G54" s="9" t="s">
+      <c r="F54" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="H54" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I54" s="9" t="s">
+      <c r="I54" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="J54" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L54" s="10">
-        <f>B54*K54</f>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B55" s="9">
+      <c r="J54" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L54" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="6">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="7">
         <v>1</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" s="9" t="s">
+      <c r="F55" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I55" s="9" t="s">
+      <c r="I55" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="J55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L55" s="10">
-        <f>B55*K55</f>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B56" s="9">
+      <c r="J55" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="7">
         <v>1</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" s="9" t="s">
+      <c r="F56" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I56" s="9" t="s">
+      <c r="I56" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="J56" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L56" s="10">
-        <f>B56*K56</f>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B57" s="9">
+      <c r="J56" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="7">
         <v>1</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="F57" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H57" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I57" s="9" t="s">
+      <c r="I57" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="J57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L57" s="10">
-        <f>B57*K57</f>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B58" s="9">
+      <c r="J57" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="6">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="7">
         <v>1</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F58" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" s="9" t="s">
+      <c r="F58" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="H58" s="9" t="s">
+      <c r="H58" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I58" s="9" t="s">
+      <c r="I58" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="J58" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L58" s="10">
-        <f>B58*K58</f>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B59" s="9">
+      <c r="J58" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="6">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="7">
         <v>1</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K59" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L59" s="10">
-        <f>B59*K59</f>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B60" s="9">
+      <c r="F59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="6">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="7">
         <v>1</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K60" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L60" s="10">
-        <f>B60*K60</f>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B61" s="9">
+      <c r="F60" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L60" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A61" s="6">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="7">
         <v>1</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G61" s="9" t="s">
+      <c r="F61" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="H61" s="9" t="s">
+      <c r="H61" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="I61" s="9" t="s">
+      <c r="I61" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="J61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L61" s="10">
-        <f>B61*K61</f>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="8">
-        <f>ROW()-6</f>
-      </c>
-      <c r="B62" s="11">
+      <c r="J61" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A62" s="6">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="11" t="e">
         <f>SUM(L7:L61)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -3602,109 +3752,111 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="B62:L62"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.625" customWidth="1"/>
-    <col min="2" max="2" width="57.5" customWidth="1"/>
+    <col min="1" max="1" width="23.6328125" customWidth="1"/>
+    <col min="2" max="2" width="57.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>259</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>